--- a/data/Rivers/swed_rivers/coord_swed_riv.xlsx
+++ b/data/Rivers/swed_rivers/coord_swed_riv.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20409"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -1727,6 +1727,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b8aad7d3-4569-465e-b6db-b00f3847ad08" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CEBE5EA080DAB6418FDF4B171D3DCB62" ma:contentTypeVersion="13" ma:contentTypeDescription="Crea un document nou" ma:contentTypeScope="" ma:versionID="f99b759a94b7469098e3d95f0f87bf05">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b8aad7d3-4569-465e-b6db-b00f3847ad08" xmlns:ns4="7a05725b-432a-4f4b-8a80-b3c0b821d7de" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9315b3ad252e7d9eb1e38e301650b69" ns3:_="" ns4:_="">
     <xsd:import namespace="b8aad7d3-4569-465e-b6db-b00f3847ad08"/>
@@ -1947,24 +1964,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b8aad7d3-4569-465e-b6db-b00f3847ad08" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69942EBD-6B76-49EF-8C7E-F356ED14E35C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006A3C8F-0C37-4A49-A0BE-CCF7C40E71CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="b8aad7d3-4569-465e-b6db-b00f3847ad08"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="7a05725b-432a-4f4b-8a80-b3c0b821d7de"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BAE3991-9349-466A-8DFB-630BB81438E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1981,29 +2006,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006A3C8F-0C37-4A49-A0BE-CCF7C40E71CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b8aad7d3-4569-465e-b6db-b00f3847ad08"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7a05725b-432a-4f4b-8a80-b3c0b821d7de"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69942EBD-6B76-49EF-8C7E-F356ED14E35C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>